--- a/sources/king_step3.xlsx
+++ b/sources/king_step3.xlsx
@@ -1036,6 +1036,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1073,6 +1078,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1110,6 +1120,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1147,6 +1162,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1189,6 +1209,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1221,6 +1246,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1258,6 +1288,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1295,6 +1330,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1332,6 +1372,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1369,6 +1414,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -1406,6 +1456,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -1443,6 +1498,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -1480,6 +1540,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -1517,6 +1582,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -1564,6 +1634,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -1596,6 +1671,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -1633,6 +1713,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -1675,6 +1760,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -1712,6 +1802,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -1749,6 +1844,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -1786,6 +1886,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -1821,6 +1926,11 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -1955,6 +2065,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -1992,6 +2107,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -2029,6 +2149,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -2066,6 +2191,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -2103,6 +2233,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -2140,6 +2275,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -2177,6 +2317,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -2214,6 +2359,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -2251,6 +2401,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -2286,6 +2441,11 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -6262,6 +6422,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -6294,6 +6459,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -6331,6 +6501,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -6368,6 +6543,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -6405,6 +6585,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -6452,6 +6637,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -6489,6 +6679,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -6526,6 +6721,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -6568,6 +6768,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -6600,6 +6805,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -6637,6 +6847,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -6674,6 +6889,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="O143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -6711,6 +6931,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -6748,6 +6973,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -6785,6 +7015,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -6832,6 +7067,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -6869,6 +7109,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -6906,6 +7151,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -6943,6 +7193,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -6980,6 +7235,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -7017,6 +7277,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -7054,6 +7319,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -7091,6 +7361,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -7128,6 +7403,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -7165,6 +7445,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -7202,6 +7487,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -7239,6 +7529,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -7276,6 +7571,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -7313,6 +7613,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -7355,6 +7660,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -7397,6 +7707,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -7434,6 +7749,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -7466,6 +7786,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -7503,6 +7828,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -7540,6 +7870,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -7577,6 +7912,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -7614,6 +7954,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -7651,6 +7996,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -7688,6 +8038,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -7723,6 +8078,11 @@
       <c r="K171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -7852,6 +8212,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -7879,6 +8244,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -7906,6 +8276,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -7933,6 +8308,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -7960,6 +8340,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -7987,6 +8372,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -8014,6 +8404,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -8041,6 +8436,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -8068,6 +8468,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -8093,6 +8498,11 @@
       <c r="I184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
